--- a/docs/3S-Elite_Modbus_인터페이스_20260916.xlsx
+++ b/docs/3S-Elite_Modbus_인터페이스_20260916.xlsx
@@ -772,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>시작할 때 한 번만 읽는다 — 그 뒤 260~265 는 TCP 가 덮어쓴다</t>
+          <t>태스크는 읽기만 한다(셀마다 다시 읽는다)</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>상한 150 mm/s</t>
+          <t>306 상한 150 mm/s. 307 은 태스크가 곱하지 않는다(비율은 컨트롤러가 적용)</t>
         </is>
       </c>
     </row>
@@ -1545,12 +1545,12 @@
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>260 ~ 265</t>
+          <t>270 ~ 275</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>TCP pose (베이스 기준)</t>
+          <t>원점 pose</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
@@ -1565,73 +1565,73 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>태스크가 돌면 여기도 TCP 로 채운다</t>
+          <t>원점 확정 시 한 번 (350~355 와 같은 값)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>270 ~ 275</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>원점 pose</t>
-        </is>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>홈 위치 플래그</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>0 · 1</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>1 홈 / 0 홈 밖 (제어주기마다 갱신)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>280 ~ 285</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>원점 기준 상대좌표</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
         <is>
           <t>0.1 mm / mRad</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>원점 확정 시 한 번 (350~355 와 같은 값)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>홈 위치 플래그</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>0 · 1</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>1 홈 / 0 홈 밖 (제어주기마다 갱신)</t>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>스캔 좌표. EOAT 중심 오프셋(펜던트 eoat5_offset / eoat8_offset)을 반영한 프로브 중심 기준</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>280 ~ 285</t>
+          <t>286 / 287</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>원점 기준 상대좌표</t>
+          <t>호 위 거리 / 누적 호 길이</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -1641,24 +1641,24 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>0.1 mm / mRad</t>
+          <t>0.1 mm / mm</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>스캔 좌표. 원점이 없으면 0</t>
+          <t>TPAC 스캔 축</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>286 / 287</t>
+          <t>288 / 289</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>호 위 거리 / 누적 호 길이</t>
+          <t>눌림 상태 / 눌림 보정량</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
@@ -1668,24 +1668,24 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>0.1 mm / mm</t>
+          <t>코드 · 0.01 mm</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>TPAC 스캔 축</t>
+          <t>0 감시 안 함 / 1 적정 / 2 덜 눌림 / 3 너무 눌림</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>288 / 289</t>
+          <t>290</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>눌림 상태 / 눌림 보정량</t>
+          <t>진행 상태</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -1695,24 +1695,24 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>코드 · 0.01 mm</t>
+          <t>코드</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>0 감시 안 함 / 1 적정 / 2 덜 눌림 / 3 너무 눌림</t>
+          <t>0 대기 · 2 3점측정 · 3 원점복귀 · 4·6 스캔 · 5 완료 · 7 원점대기 · 8 적심 · 9 오류 · 10~13 마킹 · 14 차량 고정 대기</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>291 / 292</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>진행 상태</t>
+          <t>완료 줄 수 / 전체 줄 수</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -1722,24 +1722,20 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>코드</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>0 대기 · 2 3점측정 · 3 원점복귀 · 4·6 스캔 · 5 완료 · 7 원점대기 · 8 적심 · 9 오류 · 10~13 마킹 · 14 차량 고정 대기</t>
-        </is>
-      </c>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>291 / 292</t>
+          <t>293</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>완료 줄 수 / 전체 줄 수</t>
+          <t>alive 워치독</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -1749,20 +1745,24 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>제어주기마다 +1 (멈추면 발행이 끊긴 것)</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>294 / 295</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>alive 워치독</t>
+          <t>원점 확정 / 격자 완료</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -1772,24 +1772,24 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0 · 1</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>제어주기마다 +1 (멈추면 발행이 끊긴 것)</t>
+          <t>290 = 5 와 295 = 1 이 셀 완료</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>294 / 295</t>
+          <t>296 / 297 / 298</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>원점 확정 / 격자 완료</t>
+          <t>줄 간격 / 누적 이동 / 진행률</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -1799,24 +1799,24 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>0 · 1</t>
+          <t>mm · cm · %</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>290 = 5 와 295 = 1 이 셀 완료</t>
+          <t>누적 이동은 16bit 때문에 cm</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>296 / 297 / 298</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>줄 간격 / 누적 이동 / 진행률</t>
+          <t>정지 사유</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>mm · cm · %</t>
+          <t>코드</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>누적 이동은 16bit 때문에 cm</t>
+          <t>0 정상 · 1~3 프로브 접촉 실패 · 4 호 없음 · 5 마킹 실패 · 6 눌림 유지 실패 · 7 역기구학 해 없음 · 8 차량 고정 확인 시간 초과</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>300 ~ 302</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>정지 사유</t>
+          <t>3점 측정 X (중앙 / 좌 / 우)</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
@@ -1853,24 +1853,24 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>코드</t>
+          <t>0.1 mm</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>0 정상 · 1~3 프로브 접촉 실패 · 4 호 없음 · 5 마킹 실패 · 6 눌림 유지 실패 · 7 역기구학 해 없음 · 8 차량 고정 확인 시간 초과</t>
+          <t>벽면 2차식의 세 점</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>300 ~ 302</t>
+          <t>303</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>3점 측정 X (중앙 / 좌 / 우)</t>
+          <t>적정 눌림 보정량</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
@@ -1885,19 +1885,19 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>벽면 2차식의 세 점</t>
+          <t>중앙에서 센서로 잰 값</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>304 / 305</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>적정 눌림 보정량</t>
+          <t>측정 점 수 / 검출 점 수</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -1907,24 +1907,24 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>0.1 mm</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>중앙에서 센서로 잰 값</t>
+          <t>검출 &lt; 3 이면 보정값을 믿지 않는다</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>304 / 305</t>
+          <t>330 ~ 335</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>측정 점 수 / 검출 점 수</t>
+          <t>중앙 접점 pose</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
@@ -1934,24 +1934,24 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>0.1 mm / mRad</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>검출 &lt; 3 이면 보정값을 믿지 않는다</t>
+          <t>곡률 중심 계산용</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>330 ~ 335</t>
+          <t>340 ~ 345</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>중앙 접점 pose</t>
+          <t>우측 접점 pose</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -1964,21 +1964,17 @@
           <t>0.1 mm / mRad</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>곡률 중심 계산용</t>
-        </is>
-      </c>
+      <c r="E49" s="5" t="inlineStr"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>340 ~ 345</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>우측 접점 pose</t>
+          <t>arc_mode</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
@@ -1988,20 +1984,24 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>0.1 mm / mRad</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr"/>
+          <t>코드</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>v4 movec 전용 (v5 는 안 씀)</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>350 ~ 355</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>arc_mode</t>
+          <t>원점 pose</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
@@ -2011,37 +2011,10 @@
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>코드</t>
+          <t>0.1 mm / mRad</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>v4 movec 전용 (v5 는 안 씀)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>350 ~ 355</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t>원점 pose</t>
-        </is>
-      </c>
-      <c r="C52" s="11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>0.1 mm / mRad</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>270~275 와 같은 값</t>
         </is>

--- a/docs/3S-Elite_Modbus_인터페이스_20260916.xlsx
+++ b/docs/3S-Elite_Modbus_인터페이스_20260916.xlsx
@@ -772,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1597,41 +1597,41 @@
       </c>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>280 ~ 285</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>원점 기준 상대좌표</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>0.1 mm / mRad</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>스캔 좌표. EOAT 중심 오프셋(펜던트 eoat5_offset / eoat8_offset)을 반영한 프로브 중심 기준</t>
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>스캔 구간 (TPAC 동기 신호)</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>코드</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>0 없음 / 1 전진 스캔 / 2 줄 바꿈 상승 / 3 후진 스캔. 줄 시작·끝에서 바꾸고 sig_hold(0.25 s) 기다린 뒤 움직인다</t>
         </is>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>286 / 287</t>
+          <t>280 ~ 285</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>호 위 거리 / 누적 호 길이</t>
+          <t>원점 기준 상대좌표</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
@@ -1641,24 +1641,24 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>0.1 mm / mm</t>
+          <t>0.1 mm / mRad</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>TPAC 스캔 축</t>
+          <t>스캔 좌표. EOAT 중심 오프셋(펜던트 eoat5_offset / eoat8_offset)을 반영한 프로브 중심 기준</t>
         </is>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>288 / 289</t>
+          <t>286 / 287</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>눌림 상태 / 눌림 보정량</t>
+          <t>호 위 거리 / 누적 호 길이</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
@@ -1668,24 +1668,24 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>코드 · 0.01 mm</t>
+          <t>0.1 mm / mm</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>0 감시 안 함 / 1 적정 / 2 덜 눌림 / 3 너무 눌림</t>
+          <t>TPAC 스캔 축</t>
         </is>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>288 / 289</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>진행 상태</t>
+          <t>눌림 상태 / 눌림 보정량</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -1695,24 +1695,24 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>코드</t>
+          <t>코드 · 0.01 mm</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>0 대기 · 2 3점측정 · 3 원점복귀 · 4·6 스캔 · 5 완료 · 7 원점대기 · 8 적심 · 9 오류 · 10~13 마킹 · 14 차량 고정 대기</t>
+          <t>0 감시 안 함 / 1 적정 / 2 덜 눌림 / 3 너무 눌림</t>
         </is>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>291 / 292</t>
+          <t>290</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>완료 줄 수 / 전체 줄 수</t>
+          <t>진행 상태</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
@@ -1722,20 +1722,24 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>개</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr"/>
+          <t>코드</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>0 대기 · 2 3점측정 · 3 원점복귀 · 4·6 스캔 · 5 완료 · 7 원점대기 · 8 적심 · 9 오류 · 10~13 마킹 · 14 차량 고정 대기</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>291 / 292</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>alive 워치독</t>
+          <t>완료 줄 수 / 전체 줄 수</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
@@ -1745,24 +1749,20 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>제어주기마다 +1 (멈추면 발행이 끊긴 것)</t>
-        </is>
-      </c>
+          <t>개</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>294 / 295</t>
+          <t>293</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>원점 확정 / 격자 완료</t>
+          <t>alive 워치독</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
@@ -1772,24 +1772,24 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>0 · 1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>290 = 5 와 295 = 1 이 셀 완료</t>
+          <t>제어주기마다 +1 (멈추면 발행이 끊긴 것)</t>
         </is>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>296 / 297 / 298</t>
+          <t>294 / 295</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>줄 간격 / 누적 이동 / 진행률</t>
+          <t>원점 확정 / 격자 완료</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
@@ -1799,24 +1799,24 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>mm · cm · %</t>
+          <t>0 · 1</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>누적 이동은 16bit 때문에 cm</t>
+          <t>290 = 5 와 295 = 1 이 셀 완료</t>
         </is>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>296 / 297 / 298</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>정지 사유</t>
+          <t>줄 간격 / 누적 이동 / 진행률</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>코드</t>
+          <t>mm · cm · %</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>0 정상 · 1~3 프로브 접촉 실패 · 4 호 없음 · 5 마킹 실패 · 6 눌림 유지 실패 · 7 역기구학 해 없음 · 8 차량 고정 확인 시간 초과</t>
+          <t>누적 이동은 16bit 때문에 cm</t>
         </is>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>300 ~ 302</t>
+          <t>299</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>3점 측정 X (중앙 / 좌 / 우)</t>
+          <t>정지 사유</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
@@ -1853,24 +1853,24 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>0.1 mm</t>
+          <t>코드</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>벽면 2차식의 세 점</t>
+          <t>0 정상 · 1~3 프로브 접촉 실패 · 4 호 없음 · 5 마킹 실패 · 6 눌림 유지 실패 · 7 역기구학 해 없음 · 8 차량 고정 확인 시간 초과</t>
         </is>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>300 ~ 302</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>적정 눌림 보정량</t>
+          <t>3점 측정 X (중앙 / 좌 / 우)</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
@@ -1885,19 +1885,19 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>중앙에서 센서로 잰 값</t>
+          <t>벽면 2차식의 세 점</t>
         </is>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>304 / 305</t>
+          <t>303</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>측정 점 수 / 검출 점 수</t>
+          <t>적정 눌림 보정량</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -1907,24 +1907,24 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>개</t>
+          <t>0.1 mm</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>검출 &lt; 3 이면 보정값을 믿지 않는다</t>
+          <t>중앙에서 센서로 잰 값</t>
         </is>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>330 ~ 335</t>
+          <t>304 / 305</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>중앙 접점 pose</t>
+          <t>측정 점 수 / 검출 점 수</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
@@ -1934,24 +1934,24 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>0.1 mm / mRad</t>
+          <t>개</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>곡률 중심 계산용</t>
+          <t>검출 &lt; 3 이면 보정값을 믿지 않는다</t>
         </is>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>340 ~ 345</t>
+          <t>330 ~ 335</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>우측 접점 pose</t>
+          <t>중앙 접점 pose</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
@@ -1964,17 +1964,21 @@
           <t>0.1 mm / mRad</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>곡률 중심 계산용</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>340 ~ 345</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>arc_mode</t>
+          <t>우측 접점 pose</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
@@ -1984,37 +1988,60 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>코드</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>v4 movec 전용 (v5 는 안 씀)</t>
-        </is>
-      </c>
+          <t>0.1 mm / mRad</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="11" t="inlineStr">
         <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>arc_mode</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>코드</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>v4 movec 전용 (v5 는 안 씀)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
           <t>350 ~ 355</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>원점 pose</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
         <is>
           <t>0.1 mm / mRad</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>270~275 와 같은 값</t>
         </is>
@@ -2037,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2056,7 +2083,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>브리지는 좌표만 내준다 — 실제 TCP 또는 스캔용 좌표. TPAC 은 주소가 고정이라 UR 자리에 그대로 재현한다.</t>
+          <t>브리지는 좌표와 스캔 동기 신호를 내준다. 신호는 바뀔 때마다 50 ms 이상 유지하고, 방향·리셋이 바뀌는 동안에는 스캔을 끈다. TPAC 과 모의기(mqtt_test/tpac_encoder_sim.py)가 동시에 붙어도 된다.</t>
         </is>
       </c>
     </row>
@@ -2083,110 +2110,176 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>400 ~ 405</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>TCP pose — 스캔 좌표 (기본값)</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>280 ~ 285  원점 기준 상대좌표</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>0.1 mm / mRad</t>
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Coil 16 / Reg 1 bit 0</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>DO[0] 스캔 방향</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>277 = 1 전진 -&gt; 1, 3 후진 -&gt; 0</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>1 = Forward, 0 = Backward (0 -&gt; 1 = 라인 리셋) · FC1 과 FC3 에 같은 값</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>400 ~ 405</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>TCP pose — 절대 좌표로 바꿀 때</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>384 ~ 389  실제 TCP (베이스 기준)</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>0.1 mm / mRad</t>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Coil 17 / Reg 1 bit 1</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>DO[1] 스캔 플래그</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>277 = 1·3 이고 290 = 6 -&gt; 1</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>1 = 유효 검사 구간(펄스), 0 = 동결 (줄 바꿈·줄 끝·일시정지)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>410 ~ 415</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>둘째 블록</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>기본은 TCP 속도(로봇 400~405). '좌표만' 설정이면 같은 좌표</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>mm/s · mRad/s 또는 0.1 mm / mRad</t>
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Coil 18 / Reg 1 bit 2</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>DO[2] 호밍/초기화</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>290 = 0·2·3·5 -&gt; 1, 7·8 -&gt; 0</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>1 = 전체 카운터 리셋(격자 준비·격자 사이), 0 = 준비 완료(원점 도착)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>420 ~ 425</t>
+          <t>400 ~ 405</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>셋째 블록</t>
+          <t>TCP pose — 스캔 좌표 (기본값)</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>기본은 TCP 오프셋. '좌표만' 설정이면 같은 좌표</t>
+          <t>280 ~ 285  원점 기준 상대좌표</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>mm / mRad 또는 0.1 mm / mRad</t>
+          <t>0.1 mm / mRad</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
+          <t>400 ~ 405</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>TCP pose — 절대 좌표로 바꿀 때</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>384 ~ 389  실제 TCP (베이스 기준)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>0.1 mm / mRad</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>410 ~ 415</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>둘째 블록</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>기본은 TCP 속도(로봇 400~405). '좌표만' 설정이면 같은 좌표</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>mm/s · mRad/s 또는 0.1 mm / mRad</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>420 ~ 425</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>셋째 블록</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>기본은 TCP 오프셋. '좌표만' 설정이면 같은 좌표</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>mm / mRad 또는 0.1 mm / mRad</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>스캔 축 (C-scan)</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>286 / 287  호 위 거리 · 누적 호 길이</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>0.1 mm / mm</t>
         </is>

--- a/docs/3S-Elite_Modbus_인터페이스_20260916.xlsx
+++ b/docs/3S-Elite_Modbus_인터페이스_20260916.xlsx
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>306 상한 150 mm/s. 307 은 태스크가 곱하지 않는다(비율은 컨트롤러가 적용)</t>
+          <t>306 상한 100 mm/s(가속도 400 mm/s²). 307 은 태스크가 곱하지 않는다(비율은 컨트롤러가 적용)</t>
         </is>
       </c>
     </row>
